--- a/tinHelm/excel/Role.xlsx
+++ b/tinHelm/excel/Role.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DHXM\Documents\dice\tinHelm\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\COCOSproject\dice\tinHelm\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="29790" windowHeight="10455"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="35">
   <si>
     <t>编号【KEY】</t>
   </si>
@@ -55,6 +55,9 @@
     <t>初始卡牌</t>
   </si>
   <si>
+    <t>初始骰子数</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -76,6 +79,9 @@
     <t>originCards</t>
   </si>
   <si>
+    <t>originDice</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -85,6 +91,9 @@
     <t>array</t>
   </si>
   <si>
+    <t>any</t>
+  </si>
+  <si>
     <t>server</t>
   </si>
   <si>
@@ -101,6 +110,9 @@
   </si>
   <si>
     <t>[2001,2002,2003]</t>
+  </si>
+  <si>
+    <t>[[1,2,3,4,5,6],[1,2,3,4,5,6],[1,2,3,4,5,6],[1,2,3,4,5,6],[1,2,3,4,5,6]]</t>
   </si>
   <si>
     <t>刃少女</t>
@@ -1086,15 +1098,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="28.75" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="8" max="8" width="53.6916666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1116,111 +1129,126 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>1001</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E6">
         <v>100</v>
@@ -1229,21 +1257,24 @@
         <v>100</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>1002</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E7">
         <v>80</v>
@@ -1252,21 +1283,24 @@
         <v>80</v>
       </c>
       <c r="G7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>1003</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E8">
         <v>90</v>
@@ -1275,7 +1309,10 @@
         <v>90</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>34</v>
+      </c>
+      <c r="H8" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/tinHelm/excel/Role.xlsx
+++ b/tinHelm/excel/Role.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\COCOSproject\dice\tinHelm\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DHXM\Documents\dice\tinHelm\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="29790" windowHeight="10455"/>
+    <workbookView windowWidth="17895" windowHeight="8220"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/tinHelm/excel/Role.xlsx
+++ b/tinHelm/excel/Role.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="17895" windowHeight="8220"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -109,7 +109,7 @@
     <t>稳定的攻防角色，善于把冠面转化为护甲与追加伤害，适合第一局体验。</t>
   </si>
   <si>
-    <t>[2001,2002,2003]</t>
+    <t>[1,2,3]</t>
   </si>
   <si>
     <t>[[1,2,3,4,5,6],[1,2,3,4,5,6],[1,2,3,4,5,6],[1,2,3,4,5,6],[1,2,3,4,5,6]]</t>
@@ -124,7 +124,7 @@
     <t>偏向连续攻击与重掷，能快速打出多段小伤害，但防御更依赖操作节奏。</t>
   </si>
   <si>
-    <t>[2004,2005,2006]</t>
+    <t>[4,5,6]</t>
   </si>
   <si>
     <t>咒术游侠</t>
@@ -136,7 +136,7 @@
     <t>擅长资源和防御控制，可以更稳定地进入后期，依赖技能卡组合获胜。</t>
   </si>
   <si>
-    <t>[2007,2008,2009]</t>
+    <t>[7,8,9]</t>
   </si>
 </sst>
 </file>
@@ -1104,6 +1104,7 @@
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="28.75" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="7" max="7" width="36.7333333333333" customWidth="1"/>
     <col min="8" max="8" width="53.6916666666667" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1239,7 +1240,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
@@ -1265,7 +1266,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7">
-        <v>1002</v>
+        <v>2</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
@@ -1291,7 +1292,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8">
-        <v>1003</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
